--- a/Proyecto Interno/composicion-nut/Copia_DANE_4_DIC_2025act.xlsx
+++ b/Proyecto Interno/composicion-nut/Copia_DANE_4_DIC_2025act.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8f89820ab55adc2/Escritorio/Least-cost-diets-and-affordability/Proyecto Interno/composicion-nut/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{C02A0E10-A6D0-4B5A-90A4-0BF46E94461B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDB98D07-6DBC-4312-8910-2E8E385FED3D}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{C02A0E10-A6D0-4B5A-90A4-0BF46E94461B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA992B2C-8099-4965-B360-DDE8C8768A6B}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BD DANE IPC" sheetId="4" r:id="rId1"/>
@@ -1562,7 +1562,9 @@
     <col min="6" max="6" width="35" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.44140625" style="6" customWidth="1"/>
     <col min="8" max="8" width="15.6640625" style="6" customWidth="1"/>
-    <col min="9" max="24" width="11.44140625" style="6" customWidth="1"/>
+    <col min="9" max="10" width="11.44140625" style="6" customWidth="1"/>
+    <col min="11" max="11" width="23.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="24" width="11.44140625" style="6" customWidth="1"/>
     <col min="25" max="25" width="15.6640625" style="6" customWidth="1"/>
     <col min="26" max="27" width="15.5546875" style="6" customWidth="1"/>
     <col min="28" max="28" width="18.109375" style="6" customWidth="1"/>
@@ -2857,7 +2859,7 @@
         <v>8.3500000000000005E-2</v>
       </c>
       <c r="W13" s="17">
-        <v>1815</v>
+        <v>1.8149999999999999</v>
       </c>
       <c r="X13" s="17">
         <v>63</v>
